--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ187"/>
+  <dimension ref="A1:AZ188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8817,54 +8817,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>471548</v>
+        <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>104680</v>
+        <v>87134</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1852</v>
+        <v>1617</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grådådra</t>
+          <t>Fjällig stjälkröksvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alyssum alyssoides</t>
+          <t>Tulostoma calcareum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Jeppson &amp; al.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog (24), Öl</t>
+          <t>Galgrör, S Dörby, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>601212</v>
+        <v>601162</v>
       </c>
       <c r="R70" t="n">
-        <v>6276703</v>
+        <v>6276814</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8889,19 +8880,29 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Arkiv-Hö-Mör-0182</t>
-        </is>
-      </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Jag såg enbart en frukkropp, men hade inte tid att leta vidare så där kan naturligtvis ha funnits fler</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8916,28 +8917,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora., Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/471548</t>
+          <t>https://artportalen.se/Sighting/137267996</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>471871</v>
+        <v>471548</v>
       </c>
       <c r="B71" t="n">
         <v>104680</v>
@@ -8967,7 +8964,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8975,24 +8972,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog (24), Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>601307</v>
+        <v>601212</v>
       </c>
       <c r="R71" t="n">
-        <v>6276873</v>
+        <v>6276703</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9014,14 +9006,19 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Arkiv-Hö-Mör-0182</t>
+        </is>
+      </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9032,37 +9029,32 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>traktorväg</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Arkiv Floraväktarlokaler</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/471871</t>
+          <t>https://artportalen.se/Sighting/471548</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>473219</v>
+        <v>471871</v>
       </c>
       <c r="B72" t="n">
         <v>104680</v>
@@ -9092,7 +9084,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9111,10 +9103,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>601216</v>
+        <v>601307</v>
       </c>
       <c r="R72" t="n">
-        <v>6276667</v>
+        <v>6276873</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9141,12 +9133,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9160,7 +9152,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>traktorväg</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9181,16 +9173,16 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/473219</t>
+          <t>https://artportalen.se/Sighting/471871</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135447260</v>
+        <v>473219</v>
       </c>
       <c r="B73" t="n">
-        <v>104868</v>
+        <v>104680</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9215,20 +9207,34 @@
           <t>(L.) L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Väg 925, fyndplats 020, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>601307</v>
+        <v>601216</v>
       </c>
       <c r="R73" t="n">
-        <v>6276876</v>
+        <v>6276667</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9250,20 +9256,14 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt i blom just här i vägskäl till skogsbilväg</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9274,82 +9274,78 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135447260</t>
+          <t>https://artportalen.se/Sighting/473219</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>636681</v>
+        <v>135447260</v>
       </c>
       <c r="B74" t="n">
-        <v>100693</v>
+        <v>104868</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1888</v>
+        <v>1852</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tofsäxing</t>
+          <t>Grådådra</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Koeleria glauca</t>
+          <t>Alyssum alyssoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) DC.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog (23), Öl</t>
+          <t>Väg 925, fyndplats 020, Öl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>601286</v>
+        <v>601307</v>
       </c>
       <c r="R74" t="n">
-        <v>6276636</v>
+        <v>6276876</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9371,19 +9367,20 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Hö-Mör-3051</t>
-        </is>
-      </c>
+      <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt i blom just här i vägskäl till skogsbilväg</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9398,28 +9395,28 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Öland- Floraväktarna</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/636681</t>
+          <t>https://artportalen.se/Sighting/135447260</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>636940</v>
+        <v>636681</v>
       </c>
       <c r="B75" t="n">
         <v>100693</v>
@@ -9449,7 +9446,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9459,17 +9456,17 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog (23), Öl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>601222</v>
+        <v>601286</v>
       </c>
       <c r="R75" t="n">
-        <v>6276683</v>
+        <v>6276636</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9491,14 +9488,19 @@
           <t>Norra Möckleby</t>
         </is>
       </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Hö-Mör-3051</t>
+        </is>
+      </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9509,37 +9511,32 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Öland- Floraväktarna</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/636940</t>
+          <t>https://artportalen.se/Sighting/636681</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>637468</v>
+        <v>636940</v>
       </c>
       <c r="B76" t="n">
         <v>100693</v>
@@ -9569,7 +9566,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9579,14 +9576,14 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>talldunge mellan Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>601174</v>
+        <v>601222</v>
       </c>
       <c r="R76" t="n">
-        <v>6276841</v>
+        <v>6276683</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9613,12 +9610,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9632,7 +9629,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>f.d. banvall, kalkrik sand</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9653,13 +9650,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/637468</t>
+          <t>https://artportalen.se/Sighting/636940</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>54591847</v>
+        <v>637468</v>
       </c>
       <c r="B77" t="n">
         <v>100693</v>
@@ -9687,20 +9684,26 @@
           <t>(Spreng.) DC.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>talldunge mellan Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>601143</v>
+        <v>601174</v>
       </c>
       <c r="R77" t="n">
-        <v>6276662</v>
+        <v>6276841</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9727,12 +9730,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9746,7 +9749,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>f.d. banvall, kalkrik sand</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9767,13 +9770,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591847</t>
+          <t>https://artportalen.se/Sighting/637468</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>72696154</v>
+        <v>54591847</v>
       </c>
       <c r="B78" t="n">
         <v>100693</v>
@@ -9805,17 +9808,16 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>601173</v>
+        <v>601143</v>
       </c>
       <c r="R78" t="n">
-        <v>6276842</v>
+        <v>6276662</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9842,17 +9844,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>ganska gott om</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9861,24 +9858,23 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9888,43 +9884,44 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72696154</t>
+          <t>https://artportalen.se/Sighting/54591847</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121707046</v>
+        <v>72696154</v>
       </c>
       <c r="B79" t="n">
-        <v>92567</v>
+        <v>100693</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6031</v>
+        <v>1888</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tofsäxing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Koeleria glauca</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Spreng.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9932,13 +9929,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>601443</v>
+        <v>601173</v>
       </c>
       <c r="R79" t="n">
-        <v>6276610</v>
+        <v>6276842</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9962,12 +9959,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2018-08-13</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>ganska gott om</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9982,7 +9984,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>vid basen av tall, sandigt</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9996,19 +9998,23 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121707046</t>
+          <t>https://artportalen.se/Sighting/72696154</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>58884981</v>
+        <v>121707046</v>
       </c>
       <c r="B80" t="n">
-        <v>57950</v>
+        <v>92567</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10016,44 +10022,40 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>601246</v>
+        <v>601443</v>
       </c>
       <c r="R80" t="n">
-        <v>6276674</v>
+        <v>6276610</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10077,12 +10079,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10091,55 +10093,61 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>vid basen av tall, sandigt</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/58884981</t>
+          <t>https://artportalen.se/Sighting/121707046</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>13438719</v>
+        <v>58884981</v>
       </c>
       <c r="B81" t="n">
-        <v>45049</v>
+        <v>57950</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102021</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10147,21 +10155,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gårdby sandhed/talle, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>601163</v>
+        <v>601246</v>
       </c>
       <c r="R81" t="n">
-        <v>6276740</v>
+        <v>6276674</v>
       </c>
       <c r="S81" t="n">
         <v>50</v>
@@ -10188,12 +10194,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10208,49 +10214,49 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Stefan Lithner</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Stefan Lithner</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13438719</t>
+          <t>https://artportalen.se/Sighting/58884981</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>17012458</v>
+        <v>13438719</v>
       </c>
       <c r="B82" t="n">
-        <v>9463</v>
+        <v>45049</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102176</v>
+        <v>102021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heddyngbagge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bodilopsis sordida</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1775)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -10258,36 +10264,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Gårdby sandhed/talle, Öl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>601193</v>
+        <v>601163</v>
       </c>
       <c r="R82" t="n">
-        <v>6276727</v>
+        <v>6276740</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10311,12 +10305,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10331,49 +10325,49 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Stefan Lithner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Stefan Lithner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17012458</t>
+          <t>https://artportalen.se/Sighting/13438719</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>78025936</v>
+        <v>17012458</v>
       </c>
       <c r="B83" t="n">
-        <v>57947</v>
+        <v>9463</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102977</v>
+        <v>102176</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Heddyngbagge</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Bodilopsis sordida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1775)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10381,19 +10375,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>N Gårdby, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>601390</v>
+        <v>601193</v>
       </c>
       <c r="R83" t="n">
-        <v>6276813</v>
+        <v>6276727</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10417,22 +10428,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:11</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10447,49 +10448,49 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78025936</t>
+          <t>https://artportalen.se/Sighting/17012458</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>78025941</v>
+        <v>78025936</v>
       </c>
       <c r="B84" t="n">
-        <v>58238</v>
+        <v>57947</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10574,38 +10575,38 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78025941</t>
+          <t>https://artportalen.se/Sighting/78025936</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>78025938</v>
+        <v>78025941</v>
       </c>
       <c r="B85" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10690,38 +10691,38 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78025938</t>
+          <t>https://artportalen.se/Sighting/78025941</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>17021016</v>
+        <v>78025938</v>
       </c>
       <c r="B86" t="n">
-        <v>40503</v>
+        <v>58327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>214498</v>
+        <v>103015</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sikelsäckmal</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Coleophora lixella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Zeller, 1849</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10729,36 +10730,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>N Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>601193</v>
+        <v>601390</v>
       </c>
       <c r="R86" t="n">
-        <v>6276727</v>
+        <v>6276813</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10782,12 +10766,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10802,27 +10796,27 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Linda Johannesson, Guillaume Mercier, Alexandra Johansson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17021016</t>
+          <t>https://artportalen.se/Sighting/78025938</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102470713</v>
+        <v>17021016</v>
       </c>
       <c r="B87" t="n">
-        <v>43792</v>
+        <v>40503</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10830,21 +10824,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>215481</v>
+        <v>214498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dubbelbandat ljusmott</t>
+          <t>Sikelsäckmal</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrausta ostrinalis</t>
+          <t>Coleophora lixella</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hübner, 1796)</t>
+          <t>Zeller, 1849</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10859,7 +10853,11 @@
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10867,17 +10865,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>601267</v>
+        <v>601193</v>
       </c>
       <c r="R87" t="n">
-        <v>6276623</v>
+        <v>6276727</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10901,12 +10899,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10915,34 +10913,33 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470713</t>
+          <t>https://artportalen.se/Sighting/17021016</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>17012459</v>
+        <v>102470713</v>
       </c>
       <c r="B88" t="n">
-        <v>41758</v>
+        <v>43792</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10950,21 +10947,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>215656</v>
+        <v>215481</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rödlätt lövmätare</t>
+          <t>Dubbelbandat ljusmott</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Scopula rubiginata</t>
+          <t>Pyrausta ostrinalis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Hübner, 1796)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10979,11 +10976,7 @@
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -10991,17 +10984,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gårdby sandhed, Gårdby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>601193</v>
+        <v>601267</v>
       </c>
       <c r="R88" t="n">
-        <v>6276727</v>
+        <v>6276623</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11025,12 +11018,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2014-08-07</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11039,33 +11032,34 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>David Hammarberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17012459</t>
+          <t>https://artportalen.se/Sighting/102470713</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17012454</v>
+        <v>17012459</v>
       </c>
       <c r="B89" t="n">
-        <v>41451</v>
+        <v>41758</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11073,16 +11067,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>215683</v>
+        <v>215656</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mellanmätare</t>
+          <t>Rödlätt lövmätare</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phibalapteryx virgata</t>
+          <t>Scopula rubiginata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -11148,12 +11142,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
+          <t>2014-08-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11179,13 +11173,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17012454</t>
+          <t>https://artportalen.se/Sighting/17012459</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102470028</v>
+        <v>17012454</v>
       </c>
       <c r="B90" t="n">
         <v>41451</v>
@@ -11225,7 +11219,11 @@
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
           <t>lampa</t>
@@ -11233,17 +11231,17 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Gårdby sandhed, Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>601267</v>
+        <v>601193</v>
       </c>
       <c r="R90" t="n">
-        <v>6276623</v>
+        <v>6276727</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11267,12 +11265,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2014-08-06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11281,34 +11279,33 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>David Hammarberg, Tobias Hammarberg, Johan Södercrantz, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470028</t>
+          <t>https://artportalen.se/Sighting/17012454</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102470721</v>
+        <v>102470028</v>
       </c>
       <c r="B91" t="n">
-        <v>41667</v>
+        <v>41451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11316,24 +11313,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>215766</v>
+        <v>215683</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vägtornsmätare</t>
+          <t>Mellanmätare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Triphosa dubitata</t>
+          <t>Phibalapteryx virgata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
@@ -11415,16 +11416,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470721</t>
+          <t>https://artportalen.se/Sighting/102470028</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>102470725</v>
+        <v>102470721</v>
       </c>
       <c r="B92" t="n">
-        <v>41655</v>
+        <v>41667</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11432,28 +11433,24 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>215768</v>
+        <v>215766</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartbrun klaffmätare</t>
+          <t>Vägtornsmätare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Philereme transversata</t>
+          <t>Triphosa dubitata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
@@ -11535,16 +11532,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102470725</t>
+          <t>https://artportalen.se/Sighting/102470721</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>86918873</v>
+        <v>102470725</v>
       </c>
       <c r="B93" t="n">
-        <v>42417</v>
+        <v>41655</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11552,21 +11549,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>215920</v>
+        <v>215768</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kalkfly</t>
+          <t>Svartbrun klaffmätare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tyta luctuosa</t>
+          <t>Philereme transversata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Hufnagel, 1767)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11575,16 +11572,16 @@
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11623,12 +11620,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11655,54 +11652,71 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86918873</t>
+          <t>https://artportalen.se/Sighting/102470725</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2149811</v>
+        <v>86918873</v>
       </c>
       <c r="B94" t="n">
-        <v>111175</v>
+        <v>42417</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219677</v>
+        <v>215920</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kalkfly</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Tyta luctuosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>barrskog söder Dörby väster landsvägen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>601143</v>
+        <v>601267</v>
       </c>
       <c r="R94" t="n">
-        <v>6276792</v>
+        <v>6276623</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11726,17 +11740,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>4H5a NV</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11745,39 +11754,31 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>tallskog med lövinslag</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2149811</t>
+          <t>https://artportalen.se/Sighting/86918873</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2155460</v>
+        <v>2149811</v>
       </c>
       <c r="B95" t="n">
         <v>111175</v>
@@ -11808,14 +11809,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>tallskog mellan Gårdby-Dörby, östra delen, Öl</t>
+          <t>barrskog söder Dörby väster landsvägen, Öl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>601603</v>
+        <v>601143</v>
       </c>
       <c r="R95" t="n">
-        <v>6276691</v>
+        <v>6276792</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11842,12 +11843,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2009-10-04</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>4H5a NV</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11861,7 +11867,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog med lövinslag</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11882,13 +11888,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2155460</t>
+          <t>https://artportalen.se/Sighting/2149811</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>7176390</v>
+        <v>2155460</v>
       </c>
       <c r="B96" t="n">
         <v>111175</v>
@@ -11917,19 +11923,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>tallskog mellan Gårdby-Dörby, östra delen, Öl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>601419</v>
+        <v>601603</v>
       </c>
       <c r="R96" t="n">
-        <v>6276820</v>
+        <v>6276691</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11956,12 +11959,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2009-10-04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11972,16 +11975,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11991,13 +11999,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176390</t>
+          <t>https://artportalen.se/Sighting/2155460</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>16038415</v>
+        <v>7176390</v>
       </c>
       <c r="B97" t="n">
         <v>111175</v>
@@ -12031,14 +12039,14 @@
       <c r="L97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>601371</v>
+        <v>601419</v>
       </c>
       <c r="R97" t="n">
-        <v>6276796</v>
+        <v>6276820</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -12065,12 +12073,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12081,11 +12089,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12095,7 +12098,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12105,16 +12108,16 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038415</t>
+          <t>https://artportalen.se/Sighting/7176390</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2278736</v>
+        <v>16038415</v>
       </c>
       <c r="B98" t="n">
-        <v>99010</v>
+        <v>111175</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12122,48 +12125,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219769</v>
+        <v>219677</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>601177</v>
+        <v>601371</v>
       </c>
       <c r="R98" t="n">
-        <v>6276650</v>
+        <v>6276796</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -12190,12 +12182,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2009-06-09</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12209,18 +12201,18 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12230,16 +12222,16 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2278736</t>
+          <t>https://artportalen.se/Sighting/16038415</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2914483</v>
+        <v>2278736</v>
       </c>
       <c r="B99" t="n">
-        <v>99096</v>
+        <v>99010</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12247,37 +12239,51 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219798</v>
+        <v>219769</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gårdby norr, tallskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>601212</v>
+        <v>601177</v>
       </c>
       <c r="R99" t="n">
-        <v>6276703</v>
+        <v>6276650</v>
       </c>
       <c r="S99" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12301,12 +12307,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2007-07-21</t>
+          <t>2009-06-09</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12331,7 +12337,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12341,13 +12347,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2914483</t>
+          <t>https://artportalen.se/Sighting/2278736</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>16038422</v>
+        <v>2914483</v>
       </c>
       <c r="B100" t="n">
         <v>99096</v>
@@ -12376,22 +12382,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby norr, tallskogen, Öl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>601286</v>
+        <v>601212</v>
       </c>
       <c r="R100" t="n">
-        <v>6276666</v>
+        <v>6276703</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12415,12 +12418,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2007-07-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12434,18 +12437,18 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12455,13 +12458,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038422</t>
+          <t>https://artportalen.se/Sighting/2914483</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>16065665</v>
+        <v>16038422</v>
       </c>
       <c r="B101" t="n">
         <v>99096</v>
@@ -12491,11 +12494,7 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -12503,10 +12502,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>601222</v>
+        <v>601286</v>
       </c>
       <c r="R101" t="n">
-        <v>6276656</v>
+        <v>6276666</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12533,12 +12532,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12552,7 +12551,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -12563,7 +12562,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12573,13 +12572,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065665</t>
+          <t>https://artportalen.se/Sighting/16038422</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>54511725</v>
+        <v>16065665</v>
       </c>
       <c r="B102" t="n">
         <v>99096</v>
@@ -12621,10 +12620,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>601305</v>
+        <v>601222</v>
       </c>
       <c r="R102" t="n">
-        <v>6276660</v>
+        <v>6276656</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12651,12 +12650,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12670,18 +12669,18 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12691,13 +12690,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511725</t>
+          <t>https://artportalen.se/Sighting/16065665</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>54591834</v>
+        <v>54511725</v>
       </c>
       <c r="B103" t="n">
         <v>99096</v>
@@ -12727,7 +12726,11 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12735,10 +12738,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>601143</v>
+        <v>601305</v>
       </c>
       <c r="R103" t="n">
-        <v>6276662</v>
+        <v>6276660</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12765,17 +12768,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>liknar tallknipprot subsp. orbicularis</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12789,7 +12787,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12810,13 +12808,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591834</t>
+          <t>https://artportalen.se/Sighting/54511725</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>60656187</v>
+        <v>54591834</v>
       </c>
       <c r="B104" t="n">
         <v>99096</v>
@@ -12846,11 +12844,7 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12858,10 +12852,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>601309</v>
+        <v>601143</v>
       </c>
       <c r="R104" t="n">
-        <v>6276659</v>
+        <v>6276662</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12888,12 +12882,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2015-07-26</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>liknar tallknipprot subsp. orbicularis</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12907,18 +12906,18 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12928,13 +12927,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656187</t>
+          <t>https://artportalen.se/Sighting/54591834</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>60675953</v>
+        <v>60656187</v>
       </c>
       <c r="B105" t="n">
         <v>99096</v>
@@ -12972,14 +12971,14 @@
       <c r="L105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>601300</v>
+        <v>601309</v>
       </c>
       <c r="R105" t="n">
-        <v>6276643</v>
+        <v>6276659</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -13006,12 +13005,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13022,16 +13021,21 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -13041,13 +13045,13 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60675953</t>
+          <t>https://artportalen.se/Sighting/60656187</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>72345744</v>
+        <v>60675953</v>
       </c>
       <c r="B106" t="n">
         <v>99096</v>
@@ -13079,21 +13083,20 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby Tallskog, Gårdby sandhed väst, Öl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>601132</v>
+        <v>601300</v>
       </c>
       <c r="R106" t="n">
-        <v>6276668</v>
+        <v>6276643</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -13120,12 +13123,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2016-07-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13134,19 +13137,18 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Birgitta Davidsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Birgitta Davidsson, Gunnar Siljestrand</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13156,13 +13158,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345744</t>
+          <t>https://artportalen.se/Sighting/60675953</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>72346273</v>
+        <v>72345744</v>
       </c>
       <c r="B107" t="n">
         <v>99096</v>
@@ -13192,19 +13194,23 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>601269</v>
+        <v>601132</v>
       </c>
       <c r="R107" t="n">
-        <v>6276632</v>
+        <v>6276668</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -13267,13 +13273,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72346273</t>
+          <t>https://artportalen.se/Sighting/72345744</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>94467618</v>
+        <v>72346273</v>
       </c>
       <c r="B108" t="n">
         <v>99096</v>
@@ -13302,19 +13308,20 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>601316</v>
+        <v>601269</v>
       </c>
       <c r="R108" t="n">
-        <v>6276639</v>
+        <v>6276632</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -13341,12 +13348,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13367,19 +13374,23 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Ingela Carlström, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94467618</t>
+          <t>https://artportalen.se/Sighting/72346273</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>110458149</v>
+        <v>94467618</v>
       </c>
       <c r="B109" t="n">
         <v>99096</v>
@@ -13407,32 +13418,23 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>601270</v>
+        <v>601316</v>
       </c>
       <c r="R109" t="n">
-        <v>6276638</v>
+        <v>6276639</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13456,12 +13458,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13477,27 +13479,27 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Birgit Svensson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110458149</t>
+          <t>https://artportalen.se/Sighting/94467618</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135914235</v>
+        <v>110458149</v>
       </c>
       <c r="B110" t="n">
-        <v>99320</v>
+        <v>99096</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13524,27 +13526,30 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>601302</v>
+        <v>601270</v>
       </c>
       <c r="R110" t="n">
-        <v>6276648</v>
+        <v>6276638</v>
       </c>
       <c r="S110" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13568,22 +13573,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13592,33 +13587,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Hasse Andersson, Birgit Svensson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135914235</t>
+          <t>https://artportalen.se/Sighting/110458149</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>72345745</v>
+        <v>135914235</v>
       </c>
       <c r="B111" t="n">
-        <v>99142</v>
+        <v>99320</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13626,41 +13622,46 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>601132</v>
+        <v>601302</v>
       </c>
       <c r="R111" t="n">
-        <v>6276668</v>
+        <v>6276648</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13684,12 +13685,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13698,38 +13709,33 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Erik F Nordberg, Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345745</t>
+          <t>https://artportalen.se/Sighting/135914235</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>78964858</v>
+        <v>72345745</v>
       </c>
       <c r="B112" t="n">
-        <v>99156</v>
+        <v>99142</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13737,49 +13743,41 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Dörrby, Tallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>601274</v>
+        <v>601132</v>
       </c>
       <c r="R112" t="n">
-        <v>6276714</v>
+        <v>6276668</v>
       </c>
       <c r="S112" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13803,12 +13801,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13824,12 +13822,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Joakim Johansson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13839,13 +13837,13 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78964858</t>
+          <t>https://artportalen.se/Sighting/72345745</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>94471286</v>
+        <v>78964858</v>
       </c>
       <c r="B113" t="n">
         <v>99156</v>
@@ -13873,7 +13871,12 @@
           <t>(Custer) Rchb.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -13883,17 +13886,17 @@
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Vägkant norr om Gårdby sanshed, Öl</t>
+          <t>Dörrby, Tallskog, Öl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>601203</v>
+        <v>601274</v>
       </c>
       <c r="R113" t="n">
-        <v>6276671</v>
+        <v>6276714</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13917,22 +13920,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13948,62 +13941,73 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Joakim Johansson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94471286</t>
+          <t>https://artportalen.se/Sighting/78964858</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2674129</v>
+        <v>94471286</v>
       </c>
       <c r="B114" t="n">
-        <v>109814</v>
+        <v>99156</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220204</v>
+        <v>219875</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Vägkant norr om Gårdby sanshed, Öl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>601222</v>
+        <v>601203</v>
       </c>
       <c r="R114" t="n">
-        <v>6276683</v>
+        <v>6276671</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -14030,12 +14034,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2021-06-25</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14044,39 +14058,31 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>sandtag</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2674129</t>
+          <t>https://artportalen.se/Sighting/94471286</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>16071705</v>
+        <v>2674129</v>
       </c>
       <c r="B115" t="n">
         <v>109814</v>
@@ -14105,19 +14111,16 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>601272</v>
+        <v>601222</v>
       </c>
       <c r="R115" t="n">
-        <v>6276673</v>
+        <v>6276683</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -14144,12 +14147,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14163,18 +14166,18 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -14184,16 +14187,16 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071705</t>
+          <t>https://artportalen.se/Sighting/2674129</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135288243</v>
+        <v>16071705</v>
       </c>
       <c r="B116" t="n">
-        <v>109986</v>
+        <v>109814</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14219,19 +14222,22 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>601301</v>
+        <v>601272</v>
       </c>
       <c r="R116" t="n">
-        <v>6276866</v>
+        <v>6276673</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14255,17 +14261,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14276,75 +14277,75 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135288243</t>
+          <t>https://artportalen.se/Sighting/16071705</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>3025627</v>
+        <v>135288243</v>
       </c>
       <c r="B117" t="n">
-        <v>99118</v>
+        <v>109986</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gårdby N., Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>601256</v>
+        <v>601301</v>
       </c>
       <c r="R117" t="n">
-        <v>6276584</v>
+        <v>6276866</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14371,17 +14372,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2007-08-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Delvis överblommad</t>
+          <t>3 plantor i blom på släntkrön 2m från beläggningen(+6plantor utanför vägområdet)</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14392,37 +14393,32 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3025627</t>
+          <t>https://artportalen.se/Sighting/135288243</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3026664</v>
+        <v>3025627</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -14451,19 +14447,24 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Gårdby N., Öl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>601247</v>
+        <v>601256</v>
       </c>
       <c r="R118" t="n">
-        <v>6276600</v>
+        <v>6276584</v>
       </c>
       <c r="S118" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14487,12 +14488,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2007-08-10</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Delvis överblommad</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14512,12 +14518,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14527,13 +14533,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3026664</t>
+          <t>https://artportalen.se/Sighting/3025627</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3029119</v>
+        <v>3026664</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -14564,14 +14570,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Dörby S, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>601245</v>
+        <v>601247</v>
       </c>
       <c r="R119" t="n">
-        <v>6276602</v>
+        <v>6276600</v>
       </c>
       <c r="S119" t="n">
         <v>50</v>
@@ -14598,12 +14604,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2009-05-05</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14638,13 +14644,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029119</t>
+          <t>https://artportalen.se/Sighting/3026664</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3029132</v>
+        <v>3029119</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -14673,24 +14679,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby S, Öl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>601226</v>
+        <v>601245</v>
       </c>
       <c r="R120" t="n">
-        <v>6276599</v>
+        <v>6276602</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14714,12 +14715,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2009-05-05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14733,18 +14734,18 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>gles tallskog med enstaka lövträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -14754,13 +14755,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029132</t>
+          <t>https://artportalen.se/Sighting/3029119</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3029133</v>
+        <v>3029132</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -14789,16 +14790,21 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>601222</v>
+        <v>601226</v>
       </c>
       <c r="R121" t="n">
-        <v>6276594</v>
+        <v>6276599</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14833,11 +14839,6 @@
           <t>2009-06-03</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14870,13 +14871,13 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029133</t>
+          <t>https://artportalen.se/Sighting/3029132</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3029134</v>
+        <v>3029133</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -14911,10 +14912,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>601306</v>
+        <v>601222</v>
       </c>
       <c r="R122" t="n">
-        <v>6276718</v>
+        <v>6276594</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14949,6 +14950,11 @@
           <t>2009-06-03</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14981,13 +14987,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029134</t>
+          <t>https://artportalen.se/Sighting/3029133</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3029135</v>
+        <v>3029134</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -15022,10 +15028,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>601299</v>
+        <v>601306</v>
       </c>
       <c r="R123" t="n">
-        <v>6276716</v>
+        <v>6276718</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -15092,13 +15098,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3029135</t>
+          <t>https://artportalen.se/Sighting/3029134</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3035150</v>
+        <v>3029135</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -15126,31 +15132,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>601317</v>
+        <v>601299</v>
       </c>
       <c r="R124" t="n">
-        <v>6276750</v>
+        <v>6276716</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -15177,17 +15169,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>hotas av avverkning</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15201,7 +15188,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>gles tallskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -15222,13 +15209,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035150</t>
+          <t>https://artportalen.se/Sighting/3029135</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3035151</v>
+        <v>3035150</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -15256,10 +15243,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -15268,10 +15264,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>601326</v>
+        <v>601317</v>
       </c>
       <c r="R125" t="n">
-        <v>6276771</v>
+        <v>6276750</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -15343,13 +15339,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035151</t>
+          <t>https://artportalen.se/Sighting/3035150</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3035398</v>
+        <v>3035151</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -15385,14 +15381,14 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>601300</v>
+        <v>601326</v>
       </c>
       <c r="R126" t="n">
-        <v>6276710</v>
+        <v>6276771</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -15419,17 +15415,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>ej blommande</t>
+          <t>hotas av avverkning</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15443,7 +15439,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15464,13 +15460,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035398</t>
+          <t>https://artportalen.se/Sighting/3035151</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3035399</v>
+        <v>3035398</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -15510,10 +15506,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>601211</v>
+        <v>601300</v>
       </c>
       <c r="R127" t="n">
-        <v>6276590</v>
+        <v>6276710</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -15550,7 +15546,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>täckt av ris för avverkning</t>
+          <t>ej blommande</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15585,13 +15581,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3035399</t>
+          <t>https://artportalen.se/Sighting/3035398</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>3042763</v>
+        <v>3035399</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -15619,31 +15615,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>601285</v>
+        <v>601211</v>
       </c>
       <c r="R128" t="n">
-        <v>6276690</v>
+        <v>6276590</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15670,17 +15657,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>5 blommande, 50 bladrosetter</t>
+          <t>täckt av ris för avverkning</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15715,13 +15702,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042763</t>
+          <t>https://artportalen.se/Sighting/3035399</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3042764</v>
+        <v>3042763</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -15751,7 +15738,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15770,10 +15757,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>601259</v>
+        <v>601285</v>
       </c>
       <c r="R129" t="n">
-        <v>6276711</v>
+        <v>6276690</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15810,7 +15797,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
+          <t>5 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15845,13 +15832,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042764</t>
+          <t>https://artportalen.se/Sighting/3042763</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>3042765</v>
+        <v>3042764</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -15881,7 +15868,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15900,10 +15887,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>601330</v>
+        <v>601259</v>
       </c>
       <c r="R130" t="n">
-        <v>6276690</v>
+        <v>6276711</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15940,7 +15927,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
+          <t>1 blommande, 2 bestånd, 14 bladrosetter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15975,13 +15962,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042765</t>
+          <t>https://artportalen.se/Sighting/3042764</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>3042766</v>
+        <v>3042765</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -16011,12 +15998,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -16030,10 +16017,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>601317</v>
+        <v>601330</v>
       </c>
       <c r="R131" t="n">
-        <v>6276649</v>
+        <v>6276690</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -16070,7 +16057,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>9 blommande, 50 bladrosetter</t>
+          <t>4blommande, 55 bladrosetter, 2 bestånd</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16105,13 +16092,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3042766</t>
+          <t>https://artportalen.se/Sighting/3042765</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3052277</v>
+        <v>3042766</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -16141,29 +16128,29 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Dörby, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>601279</v>
+        <v>601317</v>
       </c>
       <c r="R132" t="n">
-        <v>6276712</v>
+        <v>6276649</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -16190,12 +16177,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
+          <t>2011-07-17</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>9 blommande, 50 bladrosetter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16209,18 +16201,18 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Sandtallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Veronika Johansson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16230,13 +16222,13 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3052277</t>
+          <t>https://artportalen.se/Sighting/3042766</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>79945652</v>
+        <v>3052277</v>
       </c>
       <c r="B133" t="n">
         <v>99118</v>
@@ -16264,28 +16256,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
+          <t>Dörby, Öl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>601267</v>
+        <v>601279</v>
       </c>
       <c r="R133" t="n">
-        <v>6276623</v>
+        <v>6276712</v>
       </c>
       <c r="S133" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16309,12 +16307,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16323,19 +16321,23 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Christer Klingstedt</t>
+          <t>Veronika Johansson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -16345,16 +16347,16 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79945652</t>
+          <t>https://artportalen.se/Sighting/3052277</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134863685</v>
+        <v>79945652</v>
       </c>
       <c r="B134" t="n">
-        <v>99342</v>
+        <v>99118</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16379,29 +16381,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Mörbylånga, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Tallskogen norr Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>601249</v>
+        <v>601267</v>
       </c>
       <c r="R134" t="n">
-        <v>6276655</v>
+        <v>6276623</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16425,22 +16426,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>07:53</t>
+          <t>2010-08-07</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16449,76 +16440,85 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kjell Stålberg</t>
+          <t>Christer Klingstedt</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kjell Stålberg, Carolina Stålberg</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Christer Klingstedt</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134863685</t>
+          <t>https://artportalen.se/Sighting/79945652</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3421658</v>
+        <v>134863685</v>
       </c>
       <c r="B135" t="n">
-        <v>106243</v>
+        <v>99342</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Övre Ålebäck N, Öl</t>
+          <t>Mörbylånga, Öl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>601247</v>
+        <v>601249</v>
       </c>
       <c r="R135" t="n">
-        <v>6276600</v>
+        <v>6276655</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16542,12 +16542,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16558,37 +16568,28 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
+          <t>Kjell Stålberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Jan-Olof Petersson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Kjell Stålberg, Carolina Stålberg</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3421658</t>
+          <t>https://artportalen.se/Sighting/134863685</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3424445</v>
+        <v>3421658</v>
       </c>
       <c r="B136" t="n">
         <v>106243</v>
@@ -16619,22 +16620,22 @@
       <c r="I136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>tallskog syd Dörby, Öl</t>
+          <t>Övre Ålebäck N, Öl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>601286</v>
+        <v>601247</v>
       </c>
       <c r="R136" t="n">
-        <v>6276626</v>
+        <v>6276600</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16658,12 +16659,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2010-07-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16677,18 +16678,18 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Jan-Olof Petersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -16698,13 +16699,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424445</t>
+          <t>https://artportalen.se/Sighting/3421658</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>3424446</v>
+        <v>3424445</v>
       </c>
       <c r="B137" t="n">
         <v>106243</v>
@@ -16744,10 +16745,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>601257</v>
+        <v>601286</v>
       </c>
       <c r="R137" t="n">
-        <v>6276610</v>
+        <v>6276626</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16814,13 +16815,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424446</t>
+          <t>https://artportalen.se/Sighting/3424445</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>3424453</v>
+        <v>3424446</v>
       </c>
       <c r="B138" t="n">
         <v>106243</v>
@@ -16851,19 +16852,19 @@
       <c r="I138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>tallskog mellan Dörby-Gårdby, Öl</t>
+          <t>tallskog syd Dörby, Öl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>601243</v>
+        <v>601257</v>
       </c>
       <c r="R138" t="n">
-        <v>6276628</v>
+        <v>6276610</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16890,12 +16891,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2010-07-31</t>
+          <t>2010-07-19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16909,7 +16910,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -16930,13 +16931,13 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3424453</t>
+          <t>https://artportalen.se/Sighting/3424446</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>3425394</v>
+        <v>3424453</v>
       </c>
       <c r="B139" t="n">
         <v>106243</v>
@@ -16972,14 +16973,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>tallskog mellan Dörby-Gårdby, Öl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>601237</v>
+        <v>601243</v>
       </c>
       <c r="R139" t="n">
-        <v>6276677</v>
+        <v>6276628</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -17006,12 +17007,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2010-07-31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17046,13 +17047,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3425394</t>
+          <t>https://artportalen.se/Sighting/3424453</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>7176385</v>
+        <v>3425394</v>
       </c>
       <c r="B140" t="n">
         <v>106243</v>
@@ -17081,19 +17082,21 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>601266</v>
+        <v>601237</v>
       </c>
       <c r="R140" t="n">
-        <v>6276652</v>
+        <v>6276677</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -17120,12 +17123,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17136,16 +17139,21 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -17155,13 +17163,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176385</t>
+          <t>https://artportalen.se/Sighting/3425394</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>16038157</v>
+        <v>7176385</v>
       </c>
       <c r="B141" t="n">
         <v>106243</v>
@@ -17195,14 +17203,14 @@
       <c r="L141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>601227</v>
+        <v>601266</v>
       </c>
       <c r="R141" t="n">
-        <v>6276593</v>
+        <v>6276652</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -17229,12 +17237,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17245,11 +17253,6 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -17259,7 +17262,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -17269,13 +17272,13 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038157</t>
+          <t>https://artportalen.se/Sighting/7176385</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16038171</v>
+        <v>16038157</v>
       </c>
       <c r="B142" t="n">
         <v>106243</v>
@@ -17305,11 +17308,7 @@
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -17317,10 +17316,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>601245</v>
+        <v>601227</v>
       </c>
       <c r="R142" t="n">
-        <v>6276638</v>
+        <v>6276593</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -17387,13 +17386,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038171</t>
+          <t>https://artportalen.se/Sighting/16038157</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>16038187</v>
+        <v>16038171</v>
       </c>
       <c r="B143" t="n">
         <v>106243</v>
@@ -17423,7 +17422,11 @@
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -17431,10 +17434,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>601269</v>
+        <v>601245</v>
       </c>
       <c r="R143" t="n">
-        <v>6276641</v>
+        <v>6276638</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -17501,13 +17504,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038187</t>
+          <t>https://artportalen.se/Sighting/16038171</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>16038207</v>
+        <v>16038187</v>
       </c>
       <c r="B144" t="n">
         <v>106243</v>
@@ -17545,10 +17548,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>601489</v>
+        <v>601269</v>
       </c>
       <c r="R144" t="n">
-        <v>6276715</v>
+        <v>6276641</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -17615,13 +17618,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038207</t>
+          <t>https://artportalen.se/Sighting/16038187</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>16038421</v>
+        <v>16038207</v>
       </c>
       <c r="B145" t="n">
         <v>106243</v>
@@ -17659,10 +17662,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>601286</v>
+        <v>601489</v>
       </c>
       <c r="R145" t="n">
-        <v>6276666</v>
+        <v>6276715</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -17729,13 +17732,13 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038421</t>
+          <t>https://artportalen.se/Sighting/16038207</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>16065773</v>
+        <v>16038421</v>
       </c>
       <c r="B146" t="n">
         <v>106243</v>
@@ -17773,10 +17776,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>601303</v>
+        <v>601286</v>
       </c>
       <c r="R146" t="n">
-        <v>6276692</v>
+        <v>6276666</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17803,12 +17806,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17822,7 +17825,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -17833,7 +17836,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -17843,13 +17846,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065773</t>
+          <t>https://artportalen.se/Sighting/16038421</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>17204730</v>
+        <v>16065773</v>
       </c>
       <c r="B147" t="n">
         <v>106243</v>
@@ -17879,22 +17882,18 @@
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>601400</v>
+        <v>601303</v>
       </c>
       <c r="R147" t="n">
-        <v>6276601</v>
+        <v>6276692</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17921,12 +17920,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17940,7 +17939,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -17961,13 +17960,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17204730</t>
+          <t>https://artportalen.se/Sighting/16065773</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>54444054</v>
+        <v>17204730</v>
       </c>
       <c r="B148" t="n">
         <v>106243</v>
@@ -17997,18 +17996,22 @@
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>601271</v>
+        <v>601400</v>
       </c>
       <c r="R148" t="n">
-        <v>6276655</v>
+        <v>6276601</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -18035,12 +18038,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18054,7 +18057,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -18075,13 +18078,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444054</t>
+          <t>https://artportalen.se/Sighting/17204730</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>54444133</v>
+        <v>54444054</v>
       </c>
       <c r="B149" t="n">
         <v>106243</v>
@@ -18119,10 +18122,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>601309</v>
+        <v>601271</v>
       </c>
       <c r="R149" t="n">
-        <v>6276695</v>
+        <v>6276655</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -18189,13 +18192,13 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444133</t>
+          <t>https://artportalen.se/Sighting/54444054</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>54444175</v>
+        <v>54444133</v>
       </c>
       <c r="B150" t="n">
         <v>106243</v>
@@ -18233,10 +18236,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>601351</v>
+        <v>601309</v>
       </c>
       <c r="R150" t="n">
-        <v>6276607</v>
+        <v>6276695</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -18303,13 +18306,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54444175</t>
+          <t>https://artportalen.se/Sighting/54444133</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>54511650</v>
+        <v>54444175</v>
       </c>
       <c r="B151" t="n">
         <v>106243</v>
@@ -18347,10 +18350,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>601215</v>
+        <v>601351</v>
       </c>
       <c r="R151" t="n">
-        <v>6276591</v>
+        <v>6276607</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -18377,12 +18380,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18396,18 +18399,18 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>tallskog på sand</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18417,13 +18420,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511650</t>
+          <t>https://artportalen.se/Sighting/54444175</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>54524712</v>
+        <v>54511650</v>
       </c>
       <c r="B152" t="n">
         <v>106243</v>
@@ -18457,17 +18460,17 @@
       <c r="L152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>NO Gårdby sandhed, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>601271</v>
+        <v>601215</v>
       </c>
       <c r="R152" t="n">
-        <v>6276640</v>
+        <v>6276591</v>
       </c>
       <c r="S152" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18491,12 +18494,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2015-07-21</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18507,16 +18510,21 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -18526,13 +18534,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54524712</t>
+          <t>https://artportalen.se/Sighting/54511650</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>58885018</v>
+        <v>54524712</v>
       </c>
       <c r="B153" t="n">
         <v>106243</v>
@@ -18566,14 +18574,14 @@
       <c r="L153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>NO Gårdby sandhed, Öl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>601246</v>
+        <v>601271</v>
       </c>
       <c r="R153" t="n">
-        <v>6276674</v>
+        <v>6276640</v>
       </c>
       <c r="S153" t="n">
         <v>50</v>
@@ -18600,12 +18608,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2016-04-12</t>
+          <t>2015-07-21</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18620,12 +18628,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Lernefalk</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -18635,13 +18643,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/58885018</t>
+          <t>https://artportalen.se/Sighting/54524712</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>66113422</v>
+        <v>58885018</v>
       </c>
       <c r="B154" t="n">
         <v>106243</v>
@@ -18671,11 +18679,7 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -18683,10 +18687,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>601321</v>
+        <v>601246</v>
       </c>
       <c r="R154" t="n">
-        <v>6276619</v>
+        <v>6276674</v>
       </c>
       <c r="S154" t="n">
         <v>50</v>
@@ -18713,12 +18717,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2017-06-04</t>
+          <t>2016-04-12</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18733,12 +18737,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Hans Lindfors</t>
+          <t>Håkan Lernefalk</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -18748,13 +18752,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66113422</t>
+          <t>https://artportalen.se/Sighting/58885018</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>66676941</v>
+        <v>66113422</v>
       </c>
       <c r="B155" t="n">
         <v>106243</v>
@@ -18784,21 +18788,25 @@
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N2, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>601276</v>
+        <v>601321</v>
       </c>
       <c r="R155" t="n">
-        <v>6276684</v>
+        <v>6276619</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18822,12 +18830,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2017-06-04</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18842,12 +18850,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Hans Lindfors</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -18857,13 +18865,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66676941</t>
+          <t>https://artportalen.se/Sighting/66113422</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>72346187</v>
+        <v>66676941</v>
       </c>
       <c r="B156" t="n">
         <v>106243</v>
@@ -18893,23 +18901,18 @@
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, N2, Öl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>601215</v>
+        <v>601276</v>
       </c>
       <c r="R156" t="n">
-        <v>6276612</v>
+        <v>6276684</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18936,12 +18939,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18950,7 +18953,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -18972,13 +18974,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72346187</t>
+          <t>https://artportalen.se/Sighting/66676941</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>86801212</v>
+        <v>72346187</v>
       </c>
       <c r="B157" t="n">
         <v>106243</v>
@@ -19010,21 +19012,21 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>601246</v>
+        <v>601215</v>
       </c>
       <c r="R157" t="n">
-        <v>6276644</v>
+        <v>6276612</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -19051,12 +19053,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19069,20 +19071,15 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -19092,16 +19089,16 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86801212</t>
+          <t>https://artportalen.se/Sighting/72346187</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>94467626</v>
+        <v>86801212</v>
       </c>
       <c r="B158" t="n">
-        <v>106244</v>
+        <v>106243</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19127,19 +19124,24 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Dörby tallskog, norr sandheden, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>601269</v>
+        <v>601246</v>
       </c>
       <c r="R158" t="n">
-        <v>6276632</v>
+        <v>6276644</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -19166,12 +19168,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19184,27 +19186,36 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94467626</t>
+          <t>https://artportalen.se/Sighting/86801212</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>99255605</v>
+        <v>94467626</v>
       </c>
       <c r="B159" t="n">
         <v>106244</v>
@@ -19232,29 +19243,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Gårdby-Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, norr sandheden, Öl</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>601203</v>
+        <v>601269</v>
       </c>
       <c r="R159" t="n">
-        <v>6276606</v>
+        <v>6276632</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -19281,12 +19283,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19299,32 +19301,27 @@
       <c r="AG159" t="b">
         <v>0</v>
       </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
-      </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255605</t>
+          <t>https://artportalen.se/Sighting/94467626</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>99255615</v>
+        <v>99255605</v>
       </c>
       <c r="B160" t="n">
         <v>106244</v>
@@ -19352,8 +19349,16 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
@@ -19363,10 +19368,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>601209</v>
+        <v>601203</v>
       </c>
       <c r="R160" t="n">
-        <v>6276612</v>
+        <v>6276606</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -19430,13 +19435,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255615</t>
+          <t>https://artportalen.se/Sighting/99255605</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>99255628</v>
+        <v>99255615</v>
       </c>
       <c r="B161" t="n">
         <v>106244</v>
@@ -19464,16 +19469,8 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
@@ -19483,10 +19480,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>601239</v>
+        <v>601209</v>
       </c>
       <c r="R161" t="n">
-        <v>6276653</v>
+        <v>6276612</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -19550,13 +19547,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255628</t>
+          <t>https://artportalen.se/Sighting/99255615</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>99255660</v>
+        <v>99255628</v>
       </c>
       <c r="B162" t="n">
         <v>106244</v>
@@ -19586,7 +19583,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -19603,10 +19600,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>601321</v>
+        <v>601239</v>
       </c>
       <c r="R162" t="n">
-        <v>6276611</v>
+        <v>6276653</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -19670,13 +19667,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99255660</t>
+          <t>https://artportalen.se/Sighting/99255628</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>101612360</v>
+        <v>99255660</v>
       </c>
       <c r="B163" t="n">
         <v>106244</v>
@@ -19704,28 +19701,32 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby-Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>601240</v>
+        <v>601321</v>
       </c>
       <c r="R163" t="n">
-        <v>6276652</v>
+        <v>6276611</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -19749,12 +19750,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19767,27 +19768,32 @@
       <c r="AG163" t="b">
         <v>0</v>
       </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Erik F Nordberg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Erik F Nordberg, Karin Andersson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101612360</t>
+          <t>https://artportalen.se/Sighting/99255660</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126780833</v>
+        <v>101612360</v>
       </c>
       <c r="B164" t="n">
         <v>106244</v>
@@ -19817,22 +19823,26 @@
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>601288</v>
+        <v>601240</v>
       </c>
       <c r="R164" t="n">
-        <v>6276671</v>
+        <v>6276652</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19856,12 +19866,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19874,85 +19884,69 @@
       <c r="AG164" t="b">
         <v>0</v>
       </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>gallrad tallskog</t>
-        </is>
-      </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Erik F Nordberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Erik F Nordberg, Karin Andersson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126780833</t>
+          <t>https://artportalen.se/Sighting/101612360</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>60656115</v>
+        <v>126780833</v>
       </c>
       <c r="B165" t="n">
-        <v>107294</v>
+        <v>106244</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221647</v>
+        <v>221144</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>601212</v>
+        <v>601288</v>
       </c>
       <c r="R165" t="n">
-        <v>6276638</v>
+        <v>6276671</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19979,12 +19973,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19993,12 +19987,13 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>gallrad tallskog</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
@@ -20012,23 +20007,19 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+      <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656115</t>
+          <t>https://artportalen.se/Sighting/126780833</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>16065673</v>
+        <v>60656115</v>
       </c>
       <c r="B166" t="n">
-        <v>107516</v>
+        <v>107294</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20036,16 +20027,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221849</v>
+        <v>221647</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -20053,9 +20044,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -20093,12 +20096,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20112,7 +20115,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
@@ -20133,13 +20136,13 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065673</t>
+          <t>https://artportalen.se/Sighting/60656115</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>54591844</v>
+        <v>16065673</v>
       </c>
       <c r="B167" t="n">
         <v>107516</v>
@@ -20177,10 +20180,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>601143</v>
+        <v>601212</v>
       </c>
       <c r="R167" t="n">
-        <v>6276662</v>
+        <v>6276638</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -20207,12 +20210,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2015-07-26</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20226,18 +20229,18 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>fd banvall, sandig</t>
+          <t>SANDTAG</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -20247,13 +20250,13 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54591844</t>
+          <t>https://artportalen.se/Sighting/16065673</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>72696139</v>
+        <v>54591844</v>
       </c>
       <c r="B168" t="n">
         <v>107516</v>
@@ -20285,17 +20288,16 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>601166</v>
+        <v>601143</v>
       </c>
       <c r="R168" t="n">
-        <v>6276823</v>
+        <v>6276662</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -20322,12 +20324,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2015-07-26</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20336,24 +20338,23 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>sandig gammal banvall</t>
+          <t>fd banvall, sandig</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20363,33 +20364,33 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72696139</t>
+          <t>https://artportalen.se/Sighting/54591844</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>4220789</v>
+        <v>72696139</v>
       </c>
       <c r="B169" t="n">
-        <v>97983</v>
+        <v>107516</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221945</v>
+        <v>221849</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -20398,16 +20399,20 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Dörby tallskog, öster vägen, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>601369</v>
+        <v>601166</v>
       </c>
       <c r="R169" t="n">
-        <v>6276502</v>
+        <v>6276823</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -20434,12 +20439,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2008-01-27</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20448,23 +20453,24 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>sandig tallskog med enstaka hassel/ek</t>
+          <t>sandig gammal banvall</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -20474,13 +20480,13 @@
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4220789</t>
+          <t>https://artportalen.se/Sighting/72696139</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>4220790</v>
+        <v>4220789</v>
       </c>
       <c r="B170" t="n">
         <v>97983</v>
@@ -20515,10 +20521,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>601392</v>
+        <v>601369</v>
       </c>
       <c r="R170" t="n">
-        <v>6276503</v>
+        <v>6276502</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -20585,13 +20591,13 @@
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4220790</t>
+          <t>https://artportalen.se/Sighting/4220789</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>7176403</v>
+        <v>4220790</v>
       </c>
       <c r="B171" t="n">
         <v>97983</v>
@@ -20620,19 +20626,16 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Dörbyskogen, Öl</t>
+          <t>Dörby tallskog, öster vägen, Öl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>601303</v>
+        <v>601392</v>
       </c>
       <c r="R171" t="n">
-        <v>6276564</v>
+        <v>6276503</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -20659,12 +20662,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2014-02-16</t>
+          <t>2008-01-27</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20675,16 +20678,21 @@
       </c>
       <c r="AG171" t="b">
         <v>0</v>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>sandig tallskog med enstaka hassel/ek</t>
+        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -20694,13 +20702,13 @@
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7176403</t>
+          <t>https://artportalen.se/Sighting/4220790</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>16065769</v>
+        <v>7176403</v>
       </c>
       <c r="B172" t="n">
         <v>97983</v>
@@ -20734,14 +20742,14 @@
       <c r="L172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörbyskogen, Öl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>601312</v>
+        <v>601303</v>
       </c>
       <c r="R172" t="n">
-        <v>6276555</v>
+        <v>6276564</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -20768,12 +20776,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2014-02-16</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20784,11 +20792,6 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
@@ -20808,38 +20811,38 @@
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16065769</t>
+          <t>https://artportalen.se/Sighting/7176403</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>60656163</v>
+        <v>16065769</v>
       </c>
       <c r="B173" t="n">
-        <v>100292</v>
+        <v>97983</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>222223</v>
+        <v>221945</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kösa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Apera spica-venti</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) P. Beauv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -20852,10 +20855,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>601222</v>
+        <v>601312</v>
       </c>
       <c r="R173" t="n">
-        <v>6276656</v>
+        <v>6276555</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20882,12 +20885,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20901,7 +20904,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>igenlagt sandtag</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -20922,16 +20925,16 @@
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656163</t>
+          <t>https://artportalen.se/Sighting/16065769</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>5144080</v>
+        <v>60656163</v>
       </c>
       <c r="B174" t="n">
-        <v>100797</v>
+        <v>100292</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20939,34 +20942,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>222617</v>
+        <v>222223</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Kösa</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Apera spica-venti</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(L.) P. Beauv.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>601216</v>
+        <v>601222</v>
       </c>
       <c r="R174" t="n">
-        <v>6276667</v>
+        <v>6276656</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -20993,12 +20999,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21012,18 +21018,18 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>igenlagt sandtag</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -21033,13 +21039,13 @@
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5144080</t>
+          <t>https://artportalen.se/Sighting/60656163</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>72345748</v>
+        <v>5144080</v>
       </c>
       <c r="B175" t="n">
         <v>100797</v>
@@ -21068,20 +21074,16 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>601132</v>
+        <v>601216</v>
       </c>
       <c r="R175" t="n">
-        <v>6276668</v>
+        <v>6276667</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -21108,12 +21110,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21122,19 +21124,23 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>sandtag</t>
+        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -21144,16 +21150,16 @@
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72345748</t>
+          <t>https://artportalen.se/Sighting/5144080</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>135288104</v>
+        <v>72345748</v>
       </c>
       <c r="B176" t="n">
-        <v>100957</v>
+        <v>100797</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21179,19 +21185,23 @@
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Vägområde, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>601301</v>
+        <v>601132</v>
       </c>
       <c r="R176" t="n">
-        <v>6276866</v>
+        <v>6276668</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21215,12 +21225,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2018-06-30</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21229,75 +21239,76 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Edvin Åhman</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Edvin Åhman, Christine Sandberg</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135288104</t>
+          <t>https://artportalen.se/Sighting/72345748</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>86801227</v>
+        <v>135288104</v>
       </c>
       <c r="B177" t="n">
-        <v>99097</v>
+        <v>100957</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>223609</v>
+        <v>222617</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Dörbytallskog, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>601308</v>
+        <v>601301</v>
       </c>
       <c r="R177" t="n">
-        <v>6276656</v>
+        <v>6276866</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -21321,12 +21332,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21335,40 +21346,34 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>gles tallskog</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+          <t>Edvin Åhman, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86801227</t>
+          <t>https://artportalen.se/Sighting/135288104</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127081837</v>
+        <v>86801227</v>
       </c>
       <c r="B178" t="n">
         <v>99097</v>
@@ -21392,32 +21397,24 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Gårdby tallskog tornet, Öl</t>
+          <t>Dörbytallskog, Öl</t>
         </is>
       </c>
       <c r="Q178" t="n">
         <v>601308</v>
       </c>
       <c r="R178" t="n">
-        <v>6276635</v>
+        <v>6276656</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21441,22 +21438,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21469,30 +21456,39 @@
       <c r="AG178" t="b">
         <v>0</v>
       </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>gles tallskog</t>
+        </is>
+      </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Rolf Kläppe</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Tommy Carlström, Anders Sandsborg, Julia Odéhn, Bengt Antonson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127081837</t>
+          <t>https://artportalen.se/Sighting/86801227</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>16071746</v>
+        <v>127081837</v>
       </c>
       <c r="B179" t="n">
-        <v>106230</v>
+        <v>99097</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21500,40 +21496,45 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>224098</v>
+        <v>223609</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Gårdby tallskog tornet, Öl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>601278</v>
+        <v>601308</v>
       </c>
       <c r="R179" t="n">
-        <v>6276674</v>
+        <v>6276635</v>
       </c>
       <c r="S179" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -21557,12 +21558,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21571,39 +21582,31 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>tallskog</t>
-        </is>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Rolf Kläppe</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Rolf Kläppe</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16071746</t>
+          <t>https://artportalen.se/Sighting/127081837</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>60656204</v>
+        <v>16071746</v>
       </c>
       <c r="B180" t="n">
         <v>106230</v>
@@ -21641,10 +21644,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>601309</v>
+        <v>601278</v>
       </c>
       <c r="R180" t="n">
-        <v>6276659</v>
+        <v>6276674</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -21671,12 +21674,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2016-07-17</t>
+          <t>2014-07-07</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21690,7 +21693,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -21711,13 +21714,13 @@
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60656204</t>
+          <t>https://artportalen.se/Sighting/16071746</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>66674736</v>
+        <v>60656204</v>
       </c>
       <c r="B181" t="n">
         <v>106230</v>
@@ -21747,22 +21750,18 @@
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Dörby tallskog, N1, Öl</t>
+          <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>601316</v>
+        <v>601309</v>
       </c>
       <c r="R181" t="n">
-        <v>6276639</v>
+        <v>6276659</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -21789,12 +21788,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2016-07-17</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21805,16 +21804,21 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -21824,52 +21828,58 @@
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66674736</t>
+          <t>https://artportalen.se/Sighting/60656204</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>6187223</v>
+        <v>66674736</v>
       </c>
       <c r="B182" t="n">
-        <v>107062</v>
+        <v>106230</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>224354</v>
+        <v>224098</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Tallskog Gårdby-Dörby, Öl</t>
+          <t>Dörby tallskog, N1, Öl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>601335</v>
+        <v>601316</v>
       </c>
       <c r="R182" t="n">
-        <v>6276698</v>
+        <v>6276639</v>
       </c>
       <c r="S182" t="n">
         <v>25</v>
@@ -21896,12 +21906,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21912,21 +21922,16 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Tommy Carlström, Ingela Carlström</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -21936,13 +21941,13 @@
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6187223</t>
+          <t>https://artportalen.se/Sighting/66674736</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>66677098</v>
+        <v>6187223</v>
       </c>
       <c r="B183" t="n">
         <v>107062</v>
@@ -21967,26 +21972,24 @@
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Dörby tallskog, infart, Öl</t>
+          <t>Tallskog Gårdby-Dörby, Öl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>601217</v>
+        <v>601335</v>
       </c>
       <c r="R183" t="n">
-        <v>6276653</v>
+        <v>6276698</v>
       </c>
       <c r="S183" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -22010,12 +22013,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2017-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22026,16 +22029,21 @@
       </c>
       <c r="AG183" t="b">
         <v>0</v>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>tallskog på sand</t>
+        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Ingela Carlström</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ingela Carlström, Tommy Carlström</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -22045,53 +22053,57 @@
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66677098</t>
+          <t>https://artportalen.se/Sighting/6187223</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>54511699</v>
+        <v>66677098</v>
       </c>
       <c r="B184" t="n">
-        <v>97985</v>
+        <v>107062</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>224363</v>
+        <v>224354</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Veronica spicata subsp. spicata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Dörby tallskog, Öl</t>
+          <t>Dörby tallskog, infart, Öl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>601285</v>
+        <v>601217</v>
       </c>
       <c r="R184" t="n">
-        <v>6276569</v>
+        <v>6276653</v>
       </c>
       <c r="S184" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -22115,12 +22127,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2015-07-20</t>
+          <t>2017-07-11</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22131,21 +22143,16 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>tallskog på sand</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ingela Carlström</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -22155,13 +22162,13 @@
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511699</t>
+          <t>https://artportalen.se/Sighting/66677098</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>54511702</v>
+        <v>54511699</v>
       </c>
       <c r="B185" t="n">
         <v>97985</v>
@@ -22195,10 +22202,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>601304</v>
+        <v>601285</v>
       </c>
       <c r="R185" t="n">
-        <v>6276567</v>
+        <v>6276569</v>
       </c>
       <c r="S185" t="n">
         <v>25</v>
@@ -22265,47 +22272,50 @@
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54511702</t>
+          <t>https://artportalen.se/Sighting/54511699</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>6247724</v>
+        <v>54511702</v>
       </c>
       <c r="B186" t="n">
-        <v>104640</v>
+        <v>97985</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>224416</v>
+        <v>224363</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>601216</v>
+        <v>601304</v>
       </c>
       <c r="R186" t="n">
-        <v>6276667</v>
+        <v>6276567</v>
       </c>
       <c r="S186" t="n">
         <v>25</v>
@@ -22332,12 +22342,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2009-06-03</t>
+          <t>2015-07-20</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22351,7 +22361,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>sandtag</t>
+          <t>tallskog på sand</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -22372,13 +22382,13 @@
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6247724</t>
+          <t>https://artportalen.se/Sighting/54511702</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>16065671</v>
+        <v>6247724</v>
       </c>
       <c r="B187" t="n">
         <v>104640</v>
@@ -22403,19 +22413,16 @@
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Dörby tallskog, Öl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>601212</v>
+        <v>601216</v>
       </c>
       <c r="R187" t="n">
-        <v>6276638</v>
+        <v>6276667</v>
       </c>
       <c r="S187" t="n">
         <v>25</v>
@@ -22442,12 +22449,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2014-07-07</t>
+          <t>2009-06-03</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22461,26 +22468,136 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>SANDTAG</t>
+          <t>sandtag</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6247724</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>16065671</v>
+      </c>
+      <c r="B188" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Dörby tallskog, Öl</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>601212</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6276638</v>
+      </c>
+      <c r="S188" t="n">
+        <v>25</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2014-07-07</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>SANDTAG</t>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX187" t="inlineStr">
+      <c r="AX188" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY187" t="inlineStr">
+      <c r="AY188" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ187" t="inlineStr">
+      <c r="AZ188" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16065671</t>
         </is>
@@ -22674,6 +22791,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87134</v>
+        <v>87144</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87144</v>
+        <v>87145</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87145</v>
+        <v>87148</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87148</v>
+        <v>87153</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87153</v>
+        <v>87164</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87164</v>
+        <v>87165</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87165</v>
+        <v>87168</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 4152-2025 artfynd.xlsx
+++ b/artfynd/A 4152-2025 artfynd.xlsx
@@ -8820,7 +8820,7 @@
         <v>137267996</v>
       </c>
       <c r="B70" t="n">
-        <v>87168</v>
+        <v>87172</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
